--- a/九龙-何文田-朗贤峰第IIB期/朗贤峰第IIB期_销控明细表.xlsx
+++ b/九龙-何文田-朗贤峰第IIB期/朗贤峰第IIB期_销控明细表.xlsx
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>12053000</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>21717</v>
+        <v>21756</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>12053000</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>21717</v>
+        <v>21756</v>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
@@ -37123,9 +37123,9 @@
       </c>
       <c r="G18" s="22" t="inlineStr">
         <is>
-          <t>F | 555呎 (2房)
+          <t>F | 554呎 (2房)
 $1205万
-$21,717/呎
+$21,756/呎
 (24年-06月-28日)</t>
         </is>
       </c>

--- a/九龙-何文田-朗贤峰第IIB期/朗贤峰第IIB期_销控明细表.xlsx
+++ b/九龙-何文田-朗贤峰第IIB期/朗贤峰第IIB期_销控明细表.xlsx
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="E170" s="4" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>7679000</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>20369</v>
+        <v>20315</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>7679000</v>
       </c>
       <c r="L170" s="5" t="n">
-        <v>20369</v>
+        <v>20315</v>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
@@ -38068,9 +38068,9 @@
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>E | 377呎 (1房)
+          <t>E | 378呎 (1房)
 $768万
-$20,369/呎
+$20,315/呎
 (24年-06月-26日)</t>
         </is>
       </c>

--- a/九龙-何文田-朗贤峰第IIB期/朗贤峰第IIB期_销控明细表.xlsx
+++ b/九龙-何文田-朗贤峰第IIB期/朗贤峰第IIB期_销控明细表.xlsx
@@ -17824,7 +17824,7 @@
         </is>
       </c>
       <c r="E278" s="4" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>7182000</v>
       </c>
       <c r="I278" s="5" t="n">
-        <v>19050</v>
+        <v>19000</v>
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>7182000</v>
       </c>
       <c r="L278" s="5" t="n">
-        <v>19050</v>
+        <v>19000</v>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
@@ -39058,9 +39058,9 @@
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>E | 377呎 (1房)
+          <t>E | 378呎 (1房)
 $718万
-$19,050/呎
+$19,000/呎
 (24年-06月-05日)</t>
         </is>
       </c>

--- a/九龙-何文田-朗贤峰第IIB期/朗贤峰第IIB期_销控明细表.xlsx
+++ b/九龙-何文田-朗贤峰第IIB期/朗贤峰第IIB期_销控明细表.xlsx
@@ -5540,7 +5540,7 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         <v>12053000</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>21756</v>
+        <v>21717</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>12053000</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>21756</v>
+        <v>21717</v>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>11651000</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>21031</v>
+        <v>20993</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>11651000</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>21031</v>
+        <v>20993</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
@@ -9694,7 +9694,7 @@
         </is>
       </c>
       <c r="E147" s="4" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>8360000</v>
       </c>
       <c r="I147" s="5" t="n">
-        <v>22116</v>
+        <v>22175</v>
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>8360000</v>
       </c>
       <c r="L147" s="5" t="n">
-        <v>22116</v>
+        <v>22175</v>
       </c>
       <c r="M147" s="3" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         <v>7801000</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>20638</v>
+        <v>20692</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>7801000</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>20638</v>
+        <v>20692</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="E170" s="4" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>7679000</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>20315</v>
+        <v>20369</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>7679000</v>
       </c>
       <c r="L170" s="5" t="n">
-        <v>20315</v>
+        <v>20369</v>
       </c>
       <c r="M170" s="3" t="inlineStr">
         <is>
@@ -12616,7 +12616,7 @@
         </is>
       </c>
       <c r="E194" s="4" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
@@ -12632,7 +12632,7 @@
         <v>7804000</v>
       </c>
       <c r="I194" s="5" t="n">
-        <v>20646</v>
+        <v>20700</v>
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>7804000</v>
       </c>
       <c r="L194" s="5" t="n">
-        <v>20646</v>
+        <v>20700</v>
       </c>
       <c r="M194" s="3" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         </is>
       </c>
       <c r="E196" s="4" t="n">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F196" s="3" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>7804000</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>20113</v>
+        <v>20165</v>
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>7804000</v>
       </c>
       <c r="L196" s="5" t="n">
-        <v>20113</v>
+        <v>20165</v>
       </c>
       <c r="M196" s="3" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         </is>
       </c>
       <c r="E199" s="4" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
@@ -12942,7 +12942,7 @@
         <v>11946000</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>22798</v>
+        <v>22754</v>
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>11946000</v>
       </c>
       <c r="L199" s="5" t="n">
-        <v>22798</v>
+        <v>22754</v>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
@@ -13360,7 +13360,7 @@
         </is>
       </c>
       <c r="E206" s="4" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F206" s="3" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>7566000</v>
       </c>
       <c r="I206" s="5" t="n">
-        <v>20016</v>
+        <v>20069</v>
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>7566000</v>
       </c>
       <c r="L206" s="5" t="n">
-        <v>20016</v>
+        <v>20069</v>
       </c>
       <c r="M206" s="3" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         </is>
       </c>
       <c r="E213" s="4" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F213" s="3" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>7569000</v>
       </c>
       <c r="I213" s="5" t="n">
-        <v>20024</v>
+        <v>20077</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
@@ -13821,7 +13821,7 @@
         <v>7569000</v>
       </c>
       <c r="L213" s="5" t="n">
-        <v>20024</v>
+        <v>20077</v>
       </c>
       <c r="M213" s="3" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         </is>
       </c>
       <c r="E214" s="4" t="n">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>7735000</v>
       </c>
       <c r="I214" s="5" t="n">
-        <v>19936</v>
+        <v>19987</v>
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>7735000</v>
       </c>
       <c r="L214" s="5" t="n">
-        <v>19936</v>
+        <v>19987</v>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         </is>
       </c>
       <c r="E247" s="4" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F247" s="3" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>11037000</v>
       </c>
       <c r="I247" s="5" t="n">
-        <v>21063</v>
+        <v>21023</v>
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>11037000</v>
       </c>
       <c r="L247" s="5" t="n">
-        <v>21063</v>
+        <v>21023</v>
       </c>
       <c r="M247" s="3" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         </is>
       </c>
       <c r="E249" s="4" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F249" s="3" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>7379000</v>
       </c>
       <c r="I249" s="5" t="n">
-        <v>19521</v>
+        <v>19573</v>
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
@@ -16053,7 +16053,7 @@
         <v>7379000</v>
       </c>
       <c r="L249" s="5" t="n">
-        <v>19521</v>
+        <v>19573</v>
       </c>
       <c r="M249" s="3" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         </is>
       </c>
       <c r="E250" s="4" t="n">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         <v>7362000</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>18974</v>
+        <v>19023</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
@@ -16115,7 +16115,7 @@
         <v>7362000</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>18974</v>
+        <v>19023</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         </is>
       </c>
       <c r="E278" s="4" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>7182000</v>
       </c>
       <c r="I278" s="5" t="n">
-        <v>19000</v>
+        <v>19050</v>
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>7182000</v>
       </c>
       <c r="L278" s="5" t="n">
-        <v>19000</v>
+        <v>19050</v>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
@@ -19940,7 +19940,7 @@
         </is>
       </c>
       <c r="E312" s="4" t="n">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F312" s="3" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>12515000</v>
       </c>
       <c r="I312" s="5" t="n">
-        <v>23748</v>
+        <v>23703</v>
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>12515000</v>
       </c>
       <c r="L312" s="5" t="n">
-        <v>23748</v>
+        <v>23703</v>
       </c>
       <c r="M312" s="3" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         </is>
       </c>
       <c r="E319" s="4" t="n">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F319" s="3" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>7520000</v>
       </c>
       <c r="I319" s="5" t="n">
-        <v>19332</v>
+        <v>19381</v>
       </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>7520000</v>
       </c>
       <c r="L319" s="5" t="n">
-        <v>19332</v>
+        <v>19381</v>
       </c>
       <c r="M319" s="3" t="inlineStr">
         <is>
@@ -21180,7 +21180,7 @@
         </is>
       </c>
       <c r="E332" s="4" t="n">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="F332" s="3" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>7720000</v>
       </c>
       <c r="I332" s="5" t="n">
-        <v>19694</v>
+        <v>19897</v>
       </c>
       <c r="J332" s="3" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>7720000</v>
       </c>
       <c r="L332" s="5" t="n">
-        <v>19694</v>
+        <v>19897</v>
       </c>
       <c r="M332" s="3" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         </is>
       </c>
       <c r="E349" s="4" t="n">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F349" s="3" t="inlineStr">
         <is>
@@ -22250,7 +22250,7 @@
         <v>7187000</v>
       </c>
       <c r="I349" s="5" t="n">
-        <v>18476</v>
+        <v>18523</v>
       </c>
       <c r="J349" s="3" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>7187000</v>
       </c>
       <c r="L349" s="5" t="n">
-        <v>18476</v>
+        <v>18523</v>
       </c>
       <c r="M349" s="3" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         </is>
       </c>
       <c r="E409" s="4" t="n">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F409" s="3" t="inlineStr">
         <is>
@@ -25970,7 +25970,7 @@
         <v>7195000</v>
       </c>
       <c r="I409" s="5" t="n">
-        <v>18496</v>
+        <v>18544</v>
       </c>
       <c r="J409" s="3" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>7195000</v>
       </c>
       <c r="L409" s="5" t="n">
-        <v>18496</v>
+        <v>18544</v>
       </c>
       <c r="M409" s="3" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         </is>
       </c>
       <c r="E480" s="4" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F480" s="3" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>7234000</v>
       </c>
       <c r="I480" s="5" t="n">
-        <v>19138</v>
+        <v>19188</v>
       </c>
       <c r="J480" s="3" t="inlineStr">
         <is>
@@ -30391,7 +30391,7 @@
         <v>7234000</v>
       </c>
       <c r="L480" s="5" t="n">
-        <v>19138</v>
+        <v>19188</v>
       </c>
       <c r="M480" s="3" t="inlineStr">
         <is>
@@ -31108,7 +31108,7 @@
         </is>
       </c>
       <c r="E492" s="4" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F492" s="3" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>7359000</v>
       </c>
       <c r="I492" s="5" t="n">
-        <v>19468</v>
+        <v>19520</v>
       </c>
       <c r="J492" s="3" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>7359000</v>
       </c>
       <c r="L492" s="5" t="n">
-        <v>19468</v>
+        <v>19520</v>
       </c>
       <c r="M492" s="3" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         </is>
       </c>
       <c r="E515" s="4" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F515" s="3" t="inlineStr">
         <is>
@@ -32550,7 +32550,7 @@
         <v>10400000</v>
       </c>
       <c r="I515" s="5" t="n">
-        <v>19847</v>
+        <v>19810</v>
       </c>
       <c r="J515" s="3" t="inlineStr">
         <is>
@@ -32561,7 +32561,7 @@
         <v>10400000</v>
       </c>
       <c r="L515" s="5" t="n">
-        <v>19847</v>
+        <v>19810</v>
       </c>
       <c r="M515" s="3" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         </is>
       </c>
       <c r="E552" s="4" t="n">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F552" s="3" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>7022000</v>
       </c>
       <c r="I552" s="5" t="n">
-        <v>18577</v>
+        <v>18626</v>
       </c>
       <c r="J552" s="3" t="inlineStr">
         <is>
@@ -34855,7 +34855,7 @@
         <v>7022000</v>
       </c>
       <c r="L552" s="5" t="n">
-        <v>18577</v>
+        <v>18626</v>
       </c>
       <c r="M552" s="3" t="inlineStr">
         <is>
@@ -37123,9 +37123,9 @@
       </c>
       <c r="G18" s="22" t="inlineStr">
         <is>
-          <t>F | 554呎 (2房)
+          <t>F | 555呎 (2房)
 $1205万
-$21,756/呎
+$21,717/呎
 (24年-06月-28日)</t>
         </is>
       </c>
@@ -37233,9 +37233,9 @@
       </c>
       <c r="G20" s="22" t="inlineStr">
         <is>
-          <t>F | 554呎 (2房)
+          <t>F | 555呎 (2房)
 $1165万
-$21,031/呎
+$20,993/呎
 (24年-05月-27日)</t>
         </is>
       </c>
@@ -37848,9 +37848,9 @@
       </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
-          <t>E | 378呎 (1房)
+          <t>E | 377呎 (1房)
 $836万
-$22,116/呎
+$22,175/呎
 (24年-05月-28日)</t>
         </is>
       </c>
@@ -37903,9 +37903,9 @@
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t>E | 378呎 (1房)
+          <t>E | 377呎 (1房)
 $780万
-$20,638/呎
+$20,692/呎
 (24年-05月-27日)</t>
         </is>
       </c>
@@ -38068,9 +38068,9 @@
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>E | 378呎 (1房)
+          <t>E | 377呎 (1房)
 $768万
-$20,315/呎
+$20,369/呎
 (24年-06月-26日)</t>
         </is>
       </c>
@@ -38272,9 +38272,9 @@
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>C | 388呎 (1房)
+          <t>C | 387呎 (1房)
 $780万
-$20,113/呎
+$20,165/呎
 (24年-05月-28日)</t>
         </is>
       </c>
@@ -38288,9 +38288,9 @@
       </c>
       <c r="F13" s="22" t="inlineStr">
         <is>
-          <t>E | 378呎 (1房)
+          <t>E | 377呎 (1房)
 $780万
-$20,646/呎
+$20,700/呎
 (24年-05月-29日)</t>
         </is>
       </c>
@@ -38351,9 +38351,9 @@
       </c>
       <c r="G14" s="22" t="inlineStr">
         <is>
-          <t>F | 524呎 (2房)
+          <t>F | 525呎 (2房)
 $1195万
-$22,798/呎
+$22,754/呎
 (24年-05月-29日)</t>
         </is>
       </c>
@@ -38398,9 +38398,9 @@
       </c>
       <c r="F15" s="22" t="inlineStr">
         <is>
-          <t>E | 378呎 (1房)
+          <t>E | 377呎 (1房)
 $757万
-$20,016/呎
+$20,069/呎
 (24年-05月-29日)</t>
         </is>
       </c>
@@ -38437,17 +38437,17 @@
       </c>
       <c r="D16" s="22" t="inlineStr">
         <is>
-          <t>C | 388呎 (1房)
+          <t>C | 387呎 (1房)
 $774万
-$19,936/呎
+$19,987/呎
 (24年-07月-03日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>D | 378呎 (1房)
+          <t>D | 377呎 (1房)
 $757万
-$20,024/呎
+$20,077/呎
 (24年-07月-03日)</t>
         </is>
       </c>
@@ -38767,17 +38767,17 @@
       </c>
       <c r="D22" s="22" t="inlineStr">
         <is>
-          <t>C | 388呎 (1房)
+          <t>C | 387呎 (1房)
 $736万
-$18,974/呎
+$19,023/呎
 (24年-05月-28日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>D | 378呎 (1房)
+          <t>D | 377呎 (1房)
 $738万
-$19,521/呎
+$19,573/呎
 (24年-05月-28日)</t>
         </is>
       </c>
@@ -38791,9 +38791,9 @@
       </c>
       <c r="G22" s="22" t="inlineStr">
         <is>
-          <t>F | 524呎 (2房)
+          <t>F | 525呎 (2房)
 $1104万
-$21,063/呎
+$21,023/呎
 (24年-05月-28日)</t>
         </is>
       </c>
@@ -39058,9 +39058,9 @@
       </c>
       <c r="F27" s="22" t="inlineStr">
         <is>
-          <t>E | 378呎 (1房)
+          <t>E | 377呎 (1房)
 $718万
-$19,000/呎
+$19,050/呎
 (24年-06月-05日)</t>
         </is>
       </c>
@@ -39524,9 +39524,9 @@
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t>F | 527呎 (2房)
+          <t>F | 528呎 (2房)
 $1252万
-$23,748/呎
+$23,703/呎
 (24年-06月-13日)</t>
         </is>
       </c>
@@ -39571,9 +39571,9 @@
       </c>
       <c r="F10" s="22" t="inlineStr">
         <is>
-          <t>E | 389呎 (1房)
+          <t>E | 388呎 (1房)
 $752万
-$19,332/呎
+$19,381/呎
 (24年-05月-22日)</t>
         </is>
       </c>
@@ -39673,9 +39673,9 @@
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>D | 392呎 (1房)
+          <t>D | 388呎 (1房)
 $772万
-$19,694/呎
+$19,897/呎
 (24年-05月-20日)</t>
         </is>
       </c>
@@ -39846,9 +39846,9 @@
       </c>
       <c r="F15" s="22" t="inlineStr">
         <is>
-          <t>E | 389呎 (1房)
+          <t>E | 388呎 (1房)
 $719万
-$18,476/呎
+$18,523/呎
 (24年-05月-27日)</t>
         </is>
       </c>
@@ -40396,9 +40396,9 @@
       </c>
       <c r="F25" s="22" t="inlineStr">
         <is>
-          <t>E | 389呎 (1房)
+          <t>E | 388呎 (1房)
 $720万
-$18,496/呎
+$18,544/呎
 (24年-05月-23日)</t>
         </is>
       </c>
@@ -41184,9 +41184,9 @@
       </c>
       <c r="F13" s="22" t="inlineStr">
         <is>
-          <t>E | 378呎 (1房)
+          <t>E | 377呎 (1房)
 $723万
-$19,138/呎
+$19,188/呎
 (24年-05月-23日)</t>
         </is>
       </c>
@@ -41294,9 +41294,9 @@
       </c>
       <c r="F15" s="22" t="inlineStr">
         <is>
-          <t>E | 378呎 (1房)
+          <t>E | 377呎 (1房)
 $736万
-$19,468/呎
+$19,520/呎
 (24年-05月-21日)</t>
         </is>
       </c>
@@ -41522,9 +41522,9 @@
       </c>
       <c r="G19" s="22" t="inlineStr">
         <is>
-          <t>F | 524呎 (2房)
+          <t>F | 525呎 (2房)
 $1040万
-$19,847/呎
+$19,810/呎
 (24年-05月-20日)</t>
         </is>
       </c>
@@ -41844,9 +41844,9 @@
       </c>
       <c r="F25" s="22" t="inlineStr">
         <is>
-          <t>E | 378呎 (1房)
+          <t>E | 377呎 (1房)
 $702万
-$18,577/呎
+$18,626/呎
 (24年-05月-23日)</t>
         </is>
       </c>
